--- a/Templates/bulkImport/config/construct_SD_config_sabah.xlsx
+++ b/Templates/bulkImport/config/construct_SD_config_sabah.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25225"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\inetpub\wwwroot\ri_kkr_new\Templates\bulkImport\config\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EB81B6-8027-4469-8808-76B3487EB738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,24 +18,11 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="68">
   <si>
     <t>*</t>
   </si>
@@ -70,6 +63,9 @@
     <t>c_remarks</t>
   </si>
   <si>
+    <t>c_workflow</t>
+  </si>
+  <si>
     <t>c_action</t>
   </si>
   <si>
@@ -121,12 +117,18 @@
     <t>c_acknowledge_company</t>
   </si>
   <si>
+    <t>c_acknowledge_signature</t>
+  </si>
+  <si>
     <t>c_acknowledge_time</t>
   </si>
   <si>
     <t>c_acknowledge_date</t>
   </si>
   <si>
+    <t>c_acknowledge_action</t>
+  </si>
+  <si>
     <t>c_respond_remark</t>
   </si>
   <si>
@@ -160,6 +162,9 @@
     <t>Remarks</t>
   </si>
   <si>
+    <t>Workflow</t>
+  </si>
+  <si>
     <t>Action</t>
   </si>
   <si>
@@ -178,12 +183,12 @@
     <t>Issued Date</t>
   </si>
   <si>
+    <t>Issue Attachment(s)</t>
+  </si>
+  <si>
     <t>Issue Remarks</t>
   </si>
   <si>
-    <t>Issue Attachment(s)</t>
-  </si>
-  <si>
     <t>Issue Action</t>
   </si>
   <si>
@@ -208,185 +213,33 @@
     <t>Acknowledge Time</t>
   </si>
   <si>
+    <t>Acknowledge Signature</t>
+  </si>
+  <si>
     <t>Acknowledge Date</t>
   </si>
   <si>
+    <t>Acknowledge Action</t>
+  </si>
+  <si>
+    <t>Respond Attachment(s)</t>
+  </si>
+  <si>
     <t>Respond Remark</t>
-  </si>
-  <si>
-    <t>Respond Attachment(s)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -394,193 +247,10 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -588,310 +258,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1178,50 +564,49 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AD5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AG5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.8518518518519" customWidth="1"/>
-    <col min="2" max="2" width="14.712962962963" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="9.28703703703704" customWidth="1"/>
-    <col min="5" max="5" width="12.8518518518519" customWidth="1"/>
-    <col min="6" max="6" width="13.8518518518519" customWidth="1"/>
-    <col min="7" max="7" width="14.287037037037" customWidth="1"/>
-    <col min="8" max="8" width="16.1388888888889" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="8.66666666666667" customWidth="1"/>
-    <col min="11" max="11" width="10.4444444444444" customWidth="1"/>
-    <col min="12" max="12" width="13.7777777777778" customWidth="1"/>
-    <col min="13" max="13" width="6.42592592592593" customWidth="1"/>
-    <col min="14" max="14" width="11.287037037037" customWidth="1"/>
-    <col min="15" max="15" width="11.712962962963" customWidth="1"/>
-    <col min="16" max="16" width="13.712962962963" customWidth="1"/>
-    <col min="17" max="17" width="16" customWidth="1"/>
-    <col min="18" max="18" width="18.8518518518519" customWidth="1"/>
-    <col min="19" max="19" width="17" customWidth="1"/>
-    <col min="20" max="20" width="21" customWidth="1"/>
-    <col min="21" max="21" width="25" customWidth="1"/>
-    <col min="22" max="22" width="22.287037037037" customWidth="1"/>
-    <col min="23" max="23" width="26.287037037037" customWidth="1"/>
-    <col min="24" max="24" width="20.8518518518519" customWidth="1"/>
-    <col min="25" max="25" width="23.287037037037" customWidth="1"/>
-    <col min="26" max="26" width="24" customWidth="1"/>
-    <col min="27" max="27" width="20" customWidth="1"/>
-    <col min="28" max="28" width="19.8518518518519" customWidth="1"/>
-    <col min="29" max="29" width="21.4259259259259" customWidth="1"/>
-    <col min="30" max="30" width="17.712962962963" customWidth="1"/>
-    <col min="31" max="31" width="21.712962962963" customWidth="1"/>
-    <col min="32" max="32" width="13.8518518518519" customWidth="1"/>
+    <col min="10" max="13" width="21.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="6.42578125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="11.28515625" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" customWidth="1"/>
+    <col min="17" max="17" width="13.7109375" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="19" max="19" width="18.85546875" customWidth="1"/>
+    <col min="20" max="20" width="17" customWidth="1"/>
+    <col min="21" max="21" width="21" customWidth="1"/>
+    <col min="22" max="22" width="25" customWidth="1"/>
+    <col min="23" max="23" width="22.28515625" customWidth="1"/>
+    <col min="24" max="24" width="26.28515625" customWidth="1"/>
+    <col min="25" max="25" width="20.85546875" customWidth="1"/>
+    <col min="26" max="26" width="23.28515625" customWidth="1"/>
+    <col min="27" max="27" width="24" customWidth="1"/>
+    <col min="28" max="28" width="24.28515625" customWidth="1"/>
+    <col min="29" max="29" width="20" customWidth="1"/>
+    <col min="30" max="30" width="19.85546875" customWidth="1"/>
+    <col min="31" max="31" width="21.42578125" customWidth="1"/>
+    <col min="32" max="32" width="17.7109375" customWidth="1"/>
+    <col min="33" max="33" width="21.7109375" customWidth="1"/>
+    <col min="34" max="34" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1238,7 +623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1266,20 +651,20 @@
       <c r="I2" t="s">
         <v>1</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="N2" t="s">
-        <v>1</v>
+      <c r="N2" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="O2" t="s">
         <v>1</v>
@@ -1294,11 +679,11 @@
         <v>1</v>
       </c>
       <c r="S2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" t="s">
         <v>3</v>
       </c>
-      <c r="T2" t="s">
-        <v>1</v>
-      </c>
       <c r="U2" t="s">
         <v>1</v>
       </c>
@@ -1329,8 +714,17 @@
       <c r="AD2" t="s">
         <v>1</v>
       </c>
+      <c r="AE2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1358,19 +752,19 @@
       <c r="I3">
         <v>8</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>9</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>10</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="2">
         <v>11</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="2">
         <v>12</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="2">
         <v>13</v>
       </c>
       <c r="O3">
@@ -1421,8 +815,17 @@
       <c r="AD3">
         <v>29</v>
       </c>
+      <c r="AE3">
+        <v>30</v>
+      </c>
+      <c r="AF3">
+        <v>31</v>
+      </c>
+      <c r="AG3">
+        <v>32</v>
+      </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1432,206 +835,222 @@
       <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="Q4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R4" t="s">
+      <c r="R4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="S4" t="s">
+      <c r="S4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="T4" t="s">
+      <c r="T4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="U4" t="s">
+      <c r="U4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X4" t="s">
+      <c r="X4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Y4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="Z4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AA4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AB4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AC4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AD4" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="AE4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5" t="s">
         <v>45</v>
       </c>
-      <c r="M5" t="s">
+      <c r="J5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N5" t="s">
-        <v>43</v>
+      <c r="K5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="O5" t="s">
         <v>47</v>
       </c>
       <c r="P5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="Q5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="R5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="S5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="V5" t="s">
         <v>53</v>
       </c>
       <c r="W5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="X5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="Y5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="Z5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AB5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AC5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AD5" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>

--- a/Templates/bulkImport/config/construct_SD_config_sabah.xlsx
+++ b/Templates/bulkImport/config/construct_SD_config_sabah.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25225"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\inetpub\wwwroot\ri_kkr_new\Templates\bulkImport\config\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EB81B6-8027-4469-8808-76B3487EB738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,11 +12,24 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="62">
   <si>
     <t>*</t>
   </si>
@@ -63,9 +70,6 @@
     <t>c_remarks</t>
   </si>
   <si>
-    <t>c_workflow</t>
-  </si>
-  <si>
     <t>c_action</t>
   </si>
   <si>
@@ -117,18 +121,12 @@
     <t>c_acknowledge_company</t>
   </si>
   <si>
-    <t>c_acknowledge_signature</t>
-  </si>
-  <si>
     <t>c_acknowledge_time</t>
   </si>
   <si>
     <t>c_acknowledge_date</t>
   </si>
   <si>
-    <t>c_acknowledge_action</t>
-  </si>
-  <si>
     <t>c_respond_remark</t>
   </si>
   <si>
@@ -162,9 +160,6 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>Workflow</t>
-  </si>
-  <si>
     <t>Action</t>
   </si>
   <si>
@@ -183,12 +178,12 @@
     <t>Issued Date</t>
   </si>
   <si>
+    <t>Issue Remarks</t>
+  </si>
+  <si>
     <t>Issue Attachment(s)</t>
   </si>
   <si>
-    <t>Issue Remarks</t>
-  </si>
-  <si>
     <t>Issue Action</t>
   </si>
   <si>
@@ -213,33 +208,185 @@
     <t>Acknowledge Time</t>
   </si>
   <si>
-    <t>Acknowledge Signature</t>
-  </si>
-  <si>
     <t>Acknowledge Date</t>
   </si>
   <si>
-    <t>Acknowledge Action</t>
+    <t>Respond Remark</t>
   </si>
   <si>
     <t>Respond Attachment(s)</t>
-  </si>
-  <si>
-    <t>Respond Remark</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -247,10 +394,193 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -258,26 +588,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -564,49 +1178,50 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AD5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.8518518518519" customWidth="1"/>
+    <col min="2" max="2" width="14.712962962963" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.28703703703704" customWidth="1"/>
+    <col min="5" max="5" width="12.8518518518519" customWidth="1"/>
+    <col min="6" max="6" width="13.8518518518519" customWidth="1"/>
+    <col min="7" max="7" width="14.287037037037" customWidth="1"/>
+    <col min="8" max="8" width="16.1388888888889" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="13" width="21.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="6.42578125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" customWidth="1"/>
-    <col min="17" max="17" width="13.7109375" customWidth="1"/>
-    <col min="18" max="18" width="16" customWidth="1"/>
-    <col min="19" max="19" width="18.85546875" customWidth="1"/>
-    <col min="20" max="20" width="17" customWidth="1"/>
-    <col min="21" max="21" width="21" customWidth="1"/>
-    <col min="22" max="22" width="25" customWidth="1"/>
-    <col min="23" max="23" width="22.28515625" customWidth="1"/>
-    <col min="24" max="24" width="26.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="23.28515625" customWidth="1"/>
-    <col min="27" max="27" width="24" customWidth="1"/>
-    <col min="28" max="28" width="24.28515625" customWidth="1"/>
-    <col min="29" max="29" width="20" customWidth="1"/>
-    <col min="30" max="30" width="19.85546875" customWidth="1"/>
-    <col min="31" max="31" width="21.42578125" customWidth="1"/>
-    <col min="32" max="32" width="17.7109375" customWidth="1"/>
-    <col min="33" max="33" width="21.7109375" customWidth="1"/>
-    <col min="34" max="34" width="13.85546875" customWidth="1"/>
+    <col min="10" max="10" width="8.66666666666667" customWidth="1"/>
+    <col min="11" max="11" width="10.4444444444444" customWidth="1"/>
+    <col min="12" max="12" width="13.7777777777778" customWidth="1"/>
+    <col min="13" max="13" width="6.42592592592593" customWidth="1"/>
+    <col min="14" max="14" width="11.287037037037" customWidth="1"/>
+    <col min="15" max="15" width="11.712962962963" customWidth="1"/>
+    <col min="16" max="16" width="13.712962962963" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="18.8518518518519" customWidth="1"/>
+    <col min="19" max="19" width="17" customWidth="1"/>
+    <col min="20" max="20" width="21" customWidth="1"/>
+    <col min="21" max="21" width="25" customWidth="1"/>
+    <col min="22" max="22" width="22.287037037037" customWidth="1"/>
+    <col min="23" max="23" width="26.287037037037" customWidth="1"/>
+    <col min="24" max="24" width="20.8518518518519" customWidth="1"/>
+    <col min="25" max="25" width="23.287037037037" customWidth="1"/>
+    <col min="26" max="26" width="24" customWidth="1"/>
+    <col min="27" max="27" width="20" customWidth="1"/>
+    <col min="28" max="28" width="19.8518518518519" customWidth="1"/>
+    <col min="29" max="29" width="21.4259259259259" customWidth="1"/>
+    <col min="30" max="30" width="17.712962962963" customWidth="1"/>
+    <col min="31" max="31" width="21.712962962963" customWidth="1"/>
+    <col min="32" max="32" width="13.8518518518519" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -623,7 +1238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -651,20 +1266,20 @@
       <c r="I2" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>2</v>
+      <c r="N2" t="s">
+        <v>1</v>
       </c>
       <c r="O2" t="s">
         <v>1</v>
@@ -679,10 +1294,10 @@
         <v>1</v>
       </c>
       <c r="S2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U2" t="s">
         <v>1</v>
@@ -714,17 +1329,8 @@
       <c r="AD2" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30">
       <c r="A3">
         <v>0</v>
       </c>
@@ -752,19 +1358,19 @@
       <c r="I3">
         <v>8</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3">
         <v>9</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3">
         <v>10</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3">
         <v>11</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3">
         <v>12</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
@@ -815,17 +1421,8 @@
       <c r="AD3">
         <v>29</v>
       </c>
-      <c r="AE3">
-        <v>30</v>
-      </c>
-      <c r="AF3">
-        <v>31</v>
-      </c>
-      <c r="AG3">
-        <v>32</v>
-      </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -835,222 +1432,206 @@
       <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" t="s">
         <v>16</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" t="s">
         <v>17</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="O4" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="P4" t="s">
         <v>19</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="Q4" t="s">
         <v>20</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="R4" t="s">
         <v>21</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="S4" t="s">
         <v>22</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="T4" t="s">
         <v>23</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="U4" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="V4" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="W4" t="s">
         <v>26</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="X4" t="s">
         <v>27</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Y4" t="s">
         <v>28</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="Z4" t="s">
         <v>29</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AA4" t="s">
         <v>30</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AB4" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="1" t="s">
+      <c r="AC4" t="s">
         <v>32</v>
       </c>
-      <c r="AD4" s="1" t="s">
+      <c r="AD4" t="s">
         <v>33</v>
       </c>
-      <c r="AE4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:30">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="AF4" s="1" t="s">
+      <c r="B5" t="s">
         <v>35</v>
       </c>
-      <c r="AG4" s="1" t="s">
+      <c r="C5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="D5" t="s">
         <v>37</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E5" t="s">
         <v>38</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
         <v>39</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>41</v>
       </c>
-      <c r="F5" t="s">
+      <c r="I5" t="s">
         <v>42</v>
       </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
         <v>43</v>
       </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>44</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="M5" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>50</v>
+      <c r="N5" t="s">
+        <v>43</v>
       </c>
       <c r="O5" t="s">
         <v>47</v>
       </c>
       <c r="P5" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>49</v>
+      </c>
+      <c r="R5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S5" t="s">
         <v>51</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="T5" t="s">
         <v>52</v>
       </c>
-      <c r="R5" t="s">
-        <v>54</v>
-      </c>
-      <c r="S5" t="s">
-        <v>53</v>
-      </c>
-      <c r="T5" t="s">
-        <v>55</v>
-      </c>
       <c r="U5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="V5" t="s">
         <v>53</v>
       </c>
       <c r="W5" t="s">
+        <v>54</v>
+      </c>
+      <c r="X5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z5" t="s">
         <v>57</v>
       </c>
-      <c r="X5" t="s">
+      <c r="AA5" t="s">
         <v>58</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="AB5" t="s">
         <v>59</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AC5" t="s">
         <v>60</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AD5" t="s">
         <v>61</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>65</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
